--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104680_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104680_W25.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.077400000000001</v>
+        <v>7.7354</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0896</v>
+        <v>9.2287</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0122</v>
+        <v>-1.4933</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4995</v>
+        <v>2.4947</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2281</v>
+        <v>1.221</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2715</v>
+        <v>1.2737</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8005</v>
+        <v>4.7584</v>
       </c>
       <c r="K2" t="n">
-        <v>3.276</v>
+        <v>3.247</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5246</v>
+        <v>1.5114</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.301</v>
+        <v>-2.2637</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0315</v>
+        <v>0.6959</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5989</v>
+        <v>-0.2047</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4326</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W2" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5103</v>
+        <v>3.0517</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5649</v>
+        <v>5.6299</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.0546</v>
+        <v>-2.5782</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5044</v>
+        <v>3.5095</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4619</v>
+        <v>-0.4542</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9663</v>
+        <v>3.9638</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5418</v>
+        <v>5.5155</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0665</v>
+        <v>1.0547</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4753</v>
+        <v>4.4608</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0374</v>
+        <v>-2.0059</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5284</v>
+        <v>-1.5089</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.208</v>
+        <v>-0.6549</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5123</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2138</v>
+        <v>3.197</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.288</v>
+        <v>1.6111</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0719</v>
+        <v>3.3131</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7838</v>
+        <v>-1.702</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2928</v>
+        <v>0.2986</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7907</v>
+        <v>1.7894</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.498</v>
+        <v>-1.4908</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6748</v>
+        <v>2.6628</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5629</v>
+        <v>2.5511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3821</v>
+        <v>-2.3642</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7779</v>
+        <v>-0.4599</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.4392</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5726</v>
+        <v>0.7693</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7003</v>
+        <v>4.2766</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1277</v>
+        <v>-3.5073</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5746</v>
+        <v>4.0085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2813</v>
+        <v>1.0514</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2932</v>
+        <v>2.957</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8858</v>
+        <v>5.9422</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8485</v>
+        <v>2.3302</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>3.612</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3113</v>
+        <v>-1.9337</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5672</v>
+        <v>-1.2788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2559</v>
+        <v>-0.6549</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7752</v>
+        <v>-0.0602</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2782</v>
+        <v>-0.2998</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4969</v>
+        <v>0.2396</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>-2.7237</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4458</v>
+        <v>0.6691</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0502</v>
+        <v>1.6925</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6045</v>
+        <v>-1.0234</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0098</v>
+        <v>0.5808</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0563</v>
+        <v>0.2842</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9534</v>
+        <v>0.2966</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9677</v>
+        <v>0.8818</v>
       </c>
       <c r="K6" t="n">
-        <v>2.348</v>
+        <v>0.8446</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6197</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9579</v>
+        <v>-0.3011</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2917</v>
+        <v>-0.5604</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6663</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3787</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.2788</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1778</v>
+        <v>-0.4052</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.7317</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7317</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3589</v>
+        <v>0.4291</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3268</v>
+        <v>1.44</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9679</v>
+        <v>-1.0109</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4041</v>
+        <v>0.3941</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6062</v>
+        <v>1.5946</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2021</v>
+        <v>-1.2006</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7921</v>
+        <v>1.7702</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5038</v>
+        <v>2.4854</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.388</v>
+        <v>-1.3761</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.7177</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>-0.4879</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1657</v>
+        <v>-0.2298</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8203</v>
+        <v>-0.9069</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4312</v>
+        <v>0.4264</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2514</v>
+        <v>-1.3333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7372</v>
+        <v>0.7435</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1082</v>
+        <v>0.1118</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6917</v>
+        <v>-0.7885</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2743</v>
+        <v>-0.3703</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2147</v>
+        <v>-1.0874</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7731</v>
+        <v>0.8784</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9878</v>
+        <v>-1.9657</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2901</v>
+        <v>0.2902</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5296</v>
+        <v>1.528</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2395</v>
+        <v>-1.2378</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1904</v>
+        <v>1.1781</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9003</v>
+        <v>-0.8879</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2268</v>
+        <v>-0.1092</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1905</v>
+        <v>0.1906</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6982</v>
+        <v>-1.5385</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0759</v>
+        <v>0.254</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6224</v>
+        <v>-1.7925</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8224</v>
+        <v>-0.822</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5741</v>
+        <v>-1.5821</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7517</v>
+        <v>0.7601</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3981</v>
+        <v>2.3588</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6469</v>
+        <v>0.6163</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7512</v>
+        <v>1.7425</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2205</v>
+        <v>-3.1808</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2211</v>
+        <v>-2.1984</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9994</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2368</v>
+        <v>-0.0823</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.113</v>
+        <v>-0.7389</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8762</v>
+        <v>0.6567</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3344</v>
+        <v>-2.0242</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9381</v>
+        <v>-2.313</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3963</v>
+        <v>0.2888</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1284</v>
+        <v>-4.193</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3421</v>
+        <v>-1.9049</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7864</v>
+        <v>-2.2881</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5208</v>
+        <v>-2.8028</v>
       </c>
       <c r="K11" t="n">
-        <v>0.052</v>
+        <v>-0.5828</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5727</v>
+        <v>-2.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3923</v>
+        <v>-1.3902</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-1.3221</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7864</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1133</v>
+        <v>-0.5353</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>-0.5298</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6959</v>
+        <v>-0.0055</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>2.0212</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4879</v>
+        <v>-2.3013</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.527</v>
+        <v>-1.9458</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0391</v>
+        <v>-0.3556</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2049</v>
+        <v>-1.126</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9179</v>
+        <v>-0.3363</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.287</v>
+        <v>-0.7896</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7884</v>
+        <v>-1.5276</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5786</v>
+        <v>0.0517</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2098</v>
+        <v>-1.5793</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4166</v>
+        <v>0.4016</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3393</v>
+        <v>-0.3881</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>0.7896</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9881</v>
+        <v>-1.0859</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.4182</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2229</v>
+        <v>-0.6677</v>
       </c>
       <c r="V12" t="n">
-        <v>2.0246</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7712</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.697500000000002</v>
+        <v>6.407400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>22.467</v>
+        <v>22.8808</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.7695</v>
+        <v>-16.4734</v>
       </c>
       <c r="G13" t="n">
-        <v>6.156799999999999</v>
+        <v>6.178900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.304400000000001</v>
+        <v>3.3029</v>
       </c>
       <c r="I13" t="n">
-        <v>2.852199999999999</v>
+        <v>2.875999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>21.7905</v>
+        <v>21.582</v>
       </c>
       <c r="K13" t="n">
-        <v>15.514</v>
+        <v>15.3733</v>
       </c>
       <c r="L13" t="n">
-        <v>6.276900000000001</v>
+        <v>6.208699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.6341</v>
+        <v>-15.4031</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.2096</v>
+        <v>-12.0704</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4243</v>
+        <v>-3.332800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5366</v>
+        <v>4.5526</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.6708</v>
+        <v>-5.6907</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.1568</v>
+        <v>-4.482</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3835</v>
+        <v>-4.693899999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2268</v>
+        <v>0.2121</v>
       </c>
       <c r="V13" t="n">
-        <v>0.160700000000001</v>
+        <v>0.1578000000000004</v>
       </c>
       <c r="W13" t="n">
-        <v>11.7303</v>
+        <v>11.6836</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.5695</v>
+        <v>-11.5257</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9783</v>
+        <v>2.1194</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6715</v>
+        <v>4.0393</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6932</v>
+        <v>-1.9199</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4162</v>
+        <v>-1.4306</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9482</v>
+        <v>0.9396</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3644</v>
+        <v>-2.3702</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8108</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>3.058</v>
+        <v>3.0369</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.227</v>
+        <v>-2.2103</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1098</v>
+        <v>-2.0973</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5267</v>
+        <v>0.6897</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8075</v>
+        <v>0.2203</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7192</v>
+        <v>0.4694</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8622</v>
+        <v>2.0217</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7096</v>
+        <v>4.8636</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8474</v>
+        <v>-2.8418</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9346</v>
+        <v>-0.9223</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2945</v>
+        <v>-1.2844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2782</v>
+        <v>2.2601</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5643</v>
+        <v>0.5548</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2128</v>
+        <v>-3.1824</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8588</v>
+        <v>-1.8392</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2505</v>
+        <v>1.3993</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2461</v>
+        <v>0.4246</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0044</v>
+        <v>0.9747</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1914</v>
+        <v>1.8074</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2466</v>
+        <v>3.5617</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0551</v>
+        <v>-1.7543</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4625</v>
+        <v>1.4484</v>
       </c>
       <c r="H16" t="n">
-        <v>2.065</v>
+        <v>2.0596</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6025</v>
+        <v>-0.6111</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6823</v>
+        <v>2.6534</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3248</v>
+        <v>3.3095</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6425</v>
+        <v>-0.656</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2198</v>
+        <v>-1.205</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4564</v>
+        <v>0.18</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0305</v>
+        <v>0.3126</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0146</v>
+        <v>1.7726</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1067</v>
+        <v>4.507</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0921</v>
+        <v>-2.7344</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4227</v>
+        <v>1.4082</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6697</v>
+        <v>3.6514</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.247</v>
+        <v>-2.2432</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8673</v>
+        <v>4.8195</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5445</v>
+        <v>5.5051</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6771</v>
+        <v>-0.6856</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4446</v>
+        <v>-3.4112</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8015</v>
+        <v>-0.0163</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1825</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3811</v>
+        <v>0.6948</v>
       </c>
       <c r="V17" t="n">
-        <v>3.3422</v>
+        <v>3.3399</v>
       </c>
       <c r="W17" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="18">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4612</v>
+        <v>-0.3112</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3729</v>
+        <v>0.4852</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.834</v>
+        <v>-0.7964</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.482</v>
+        <v>-0.4819</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5167</v>
+        <v>-0.5115</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4424</v>
+        <v>0.4364</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9245</v>
+        <v>-0.9184</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0209</v>
+        <v>0.1707</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3872</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0533</v>
+        <v>-1.4969</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6661</v>
+        <v>0.7454</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1576</v>
+        <v>-1.1692</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3378</v>
+        <v>0.328</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4954</v>
+        <v>-1.4971</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6145</v>
+        <v>-0.6392</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5431</v>
+        <v>-0.53</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3242</v>
+        <v>0.3297</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>-0.0351</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3018</v>
+        <v>0.3648</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6213</v>
+        <v>-2.0358</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9882</v>
+        <v>0.1852</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6094</v>
+        <v>-2.221</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.269</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6538</v>
+        <v>-0.2357</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0333</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7583</v>
+        <v>2.2992</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>1.6892</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.61</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3294</v>
+        <v>-2.5683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-1.9249</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5891</v>
+        <v>-0.6433</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4962</v>
+        <v>0.3714</v>
       </c>
       <c r="T20" t="n">
-        <v>1.364</v>
+        <v>0.1623</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1322</v>
+        <v>0.2091</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9939</v>
+        <v>-2.1063</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5084</v>
+        <v>-0.0599</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4855</v>
+        <v>-2.0464</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7402</v>
+        <v>-0.7349</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6248</v>
+        <v>-2.6223</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8846</v>
+        <v>1.8875</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3909</v>
+        <v>1.3712</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6318</v>
+        <v>-1.645</v>
       </c>
       <c r="L21" t="n">
-        <v>3.0227</v>
+        <v>3.0162</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1311</v>
+        <v>-2.1061</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>0.907</v>
+        <v>0.7864</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6722</v>
+        <v>1.0793</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1514</v>
+        <v>-2.4588</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2153</v>
+        <v>0.0409</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3667</v>
+        <v>-2.4996</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.261</v>
+        <v>-0.5632</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2396</v>
+        <v>-0.6466</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0214</v>
+        <v>0.0835</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3233</v>
+        <v>0.7564</v>
       </c>
       <c r="K22" t="n">
-        <v>1.697</v>
+        <v>0.0862</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6263</v>
+        <v>0.6703</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5843</v>
+        <v>-1.3196</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9366</v>
+        <v>-0.7328</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5868</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2438</v>
+        <v>0.6491</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1603</v>
+        <v>0.4226</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0835</v>
+        <v>0.2265</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.248</v>
+        <v>-2.5876</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8154</v>
+        <v>-1.8359</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4326</v>
+        <v>-0.7517</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.32</v>
+        <v>-4.3216</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3924</v>
+        <v>-3.392</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9276</v>
+        <v>-0.9296</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9757</v>
+        <v>-1.9982</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5971</v>
+        <v>-1.6105</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3443</v>
+        <v>-2.3233</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1647</v>
+        <v>0.8234</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1603</v>
+        <v>0.1623</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0044</v>
+        <v>0.6611</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.881</v>
+        <v>-3.1803</v>
       </c>
       <c r="E24" t="n">
-        <v>1.836</v>
+        <v>2.1834</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.717</v>
+        <v>-5.3636</v>
       </c>
       <c r="G24" t="n">
-        <v>0.841</v>
+        <v>0.857</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6034</v>
+        <v>-1.589</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4443</v>
+        <v>2.446</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6707</v>
+        <v>2.6645</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2078</v>
+        <v>0.2068</v>
       </c>
       <c r="L24" t="n">
-        <v>2.4629</v>
+        <v>2.4576</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8298</v>
+        <v>-1.8075</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.871</v>
+        <v>-0.2045</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0363</v>
+        <v>0.2766</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.5314</v>
+        <v>-4.5157</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.5314</v>
+        <v>-4.5157</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6975</v>
+        <v>-5.710400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>16.7697</v>
+        <v>16.4736</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.4669</v>
+        <v>-22.1837</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.1565</v>
+        <v>-6.179100000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3045</v>
+        <v>-3.3029</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.852299999999999</v>
+        <v>-2.875799999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>15.634</v>
+        <v>15.403</v>
       </c>
       <c r="K25" t="n">
-        <v>12.2096</v>
+        <v>12.0703</v>
       </c>
       <c r="L25" t="n">
-        <v>3.424599999999999</v>
+        <v>3.332699999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-21.7907</v>
+        <v>-21.5821</v>
       </c>
       <c r="N25" t="n">
-        <v>-15.5141</v>
+        <v>-15.3733</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.276800000000001</v>
+        <v>-6.2087</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.536499999999999</v>
+        <v>-4.552499999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-10.2076</v>
+        <v>-10.2436</v>
       </c>
       <c r="R25" t="n">
-        <v>5.670700000000001</v>
+        <v>5.6907</v>
       </c>
       <c r="S25" t="n">
-        <v>5.156700000000001</v>
+        <v>5.1789</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2121000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>5.383399999999999</v>
+        <v>5.3909</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607000000000003</v>
+        <v>-0.1576999999999993</v>
       </c>
       <c r="W25" t="n">
-        <v>11.5694</v>
+        <v>11.5257</v>
       </c>
       <c r="X25" t="n">
-        <v>-11.7304</v>
+        <v>-11.6836</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104680_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104680_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-11.5257</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-4.5157</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104680_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-11.6836</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
